--- a/banks/W14_Kahoot匯入.xlsx
+++ b/banks/W14_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>去羧作用</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸循環</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>乙醯輔酶A</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>去羧作用</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>檸檬酸循環</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -531,17 +531,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>去羧作用</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>克氏循環</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>異檸檬酸</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>克氏循環</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>去羧作用</t>
         </is>
       </c>
       <c r="F3" s="2" t="n">
@@ -561,19 +561,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>回補反應</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>乙醯輔酶A</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>α-酮戊二酸</t>
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>草醯乙酸</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>乙醯輔酶A</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>蘋果酸</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>檸檬酸</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>兩性途徑</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>異檸檬酸</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -741,25 +741,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>草醯乙酸</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>α-酮戊二酸</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>三磷酸鳥苷</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>草醯乙酸</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -771,30 +771,30 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>蘋果酸</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>琥珀酸</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>檸檬酸</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>蘋果酸</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>異檸檬酸</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>回補反應</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>克氏循環</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>異檸檬酸</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -841,14 +841,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>蘋果酸</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
-        </is>
-      </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
           <t>克氏循環</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -876,30 +876,30 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>克氏循環</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>草醯乙酸</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>三磷酸鳥苷</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>乙醯輔酶A</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>延胡索酸</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>三磷酸鳥苷</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>乙醯輔酶A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>克氏循環</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>乙醯輔酶A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -981,30 +981,30 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>兩性途徑</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>回補反應</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>蘋果酸</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>回補反應</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>兩性途徑</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1016,14 +1016,14 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>延胡索酸</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>異檸檬酸</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>延胡索酸</t>
-        </is>
-      </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>克氏循環</t>
@@ -1040,6 +1040,146 @@
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w14_tca_labeled) 標號1這一步驟的產物是什麼?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>琥珀醯輔酶A</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>異檸檬酸</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>蘋果酸</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:w14_tca_labeled) 標號2箭頭代表哪一種產物?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>二氧化碳</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>菸鹼醯胺腺嘌呤二核苷酸</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>黃素腺嘌呤二核苷酸</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>三磷酸鳥苷</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>草醯乙酸—去氫產生GTP</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>琥珀酸—去氫產生FADH2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>α-酮戊二酸—與乙醯輔酶A縮合成檸檬酸</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸—去羧產生二氧化碳</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>檸檬酸循環每轉一圈(每1個乙醯輔酶A)共產生幾個NADH?</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>3個NADH</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>2個NADH</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>4個NADH</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>1個NADH</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
